--- a/output/pdf_financials_xlsx/SVG.xlsx
+++ b/output/pdf_financials_xlsx/SVG.xlsx
@@ -5941,52 +5941,52 @@
         <v>0.528795</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.627829</v>
+        <v>0.671849</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.711626</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.711626</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.779037</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.892075</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.892075</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.877202</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.979097</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.94935</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.94935</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.94935</v>
       </c>
     </row>
     <row r="93">
@@ -7403,49 +7403,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.079946</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.052459</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.022919</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004312</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.5786019999999999</v>
+        <v>0.5741810000000001</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.017518</v>
+        <v>0.015054</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.022535</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009313</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0221</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06579599999999999</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.682944</v>
+        <v>0.418012</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.022926</v>
+        <v>0.017467</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.144401</v>
+        <v>-0.055303</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.008177</v>
+        <v>-0.106107</v>
       </c>
     </row>
     <row r="119">
@@ -9690,7 +9690,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10068,7 +10072,11 @@
           <t>Share-based payment reserve (Notes 6 and 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10571,7 +10579,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11107,7 +11119,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12623,7 +12639,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15587,7 +15607,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SVG.xlsx
+++ b/output/pdf_financials_xlsx/SVG.xlsx
@@ -945,37 +945,37 @@
         <v>0.275874</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.07491399999999999</v>
+        <v>0.281983</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.008798</v>
+        <v>0.114685</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.015216</v>
+        <v>0.625645</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.009658</v>
+        <v>0.042971</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.012331</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.021748</v>
+        <v>0.039916</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.019413</v>
+        <v>0.149324</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.017597</v>
+        <v>0.035487</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.019359</v>
+        <v>0.036925</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.01284</v>
+        <v>0.139</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.01422</v>
+        <v>0.03832</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0.039881</v>
@@ -1011,31 +1011,31 @@
         <v>-0.114685</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.015216</v>
+        <v>-0.625645</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.009658</v>
+        <v>-0.042971</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.012331</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.021748</v>
+        <v>-0.039916</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.019413</v>
+        <v>-0.149324</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.017597</v>
+        <v>-0.035487</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.019359</v>
+        <v>-0.036925</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.01284</v>
+        <v>-0.139</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.01422</v>
+        <v>-0.03832</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.039881</v>
@@ -2442,55 +2442,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00172</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00674</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.085856</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.042003</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.004819</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001545</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002199</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.029658</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.192314</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.055706</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.060986</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.286855</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.065731</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.144728</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.184777</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.041866</v>
       </c>
     </row>
     <row r="35">
@@ -2558,55 +2558,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.054013</v>
+        <v>0.055733</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.047416</v>
+        <v>0.054156</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.055328</v>
+        <v>0.141184</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.031219</v>
+        <v>0.073222</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.020442</v>
+        <v>0.025261</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.012796</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.011182</v>
+        <v>0.012727</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.009001</v>
+        <v>0.0112</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.017855</v>
+        <v>0.047513</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.085992</v>
+        <v>0.278306</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.08365</v>
+        <v>0.139356</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.029112</v>
+        <v>0.090098</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.056407</v>
+        <v>0.343262</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.049023</v>
+        <v>0.114754</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.039018</v>
+        <v>0.183746</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.029381</v>
+        <v>0.214158</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.02476</v>
+        <v>0.066626</v>
       </c>
     </row>
     <row r="37">
@@ -3254,55 +3254,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.28215</v>
+        <v>0.28043</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.157843</v>
+        <v>0.151103</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.142463</v>
+        <v>0.056607</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.076807</v>
+        <v>0.034804</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.018125</v>
+        <v>0.013306</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.012294</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.007218</v>
+        <v>0.005673</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.002199</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.029658</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.192314</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.057275</v>
+        <v>0.001569</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.060986</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.366029</v>
+        <v>0.07917399999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.069804</v>
+        <v>0.004073</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.147923</v>
+        <v>0.003195</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.188158</v>
+        <v>0.003381</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.045247</v>
+        <v>0.003381</v>
       </c>
     </row>
     <row r="49">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9006,7 +9006,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10173,7 +10177,11 @@
           <t>Reclamation deposits (Note 4(d))</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10678,7 +10686,11 @@
           <t>Reclamation deposits (Note 5(d))</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11740,7 +11752,11 @@
           <t>Reclamation deposits (Note 5(g))</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11938,7 +11954,11 @@
           <t>Reclamation deposits (Note 5(f))</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13148,7 +13168,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -20296,7 +20316,11 @@
           <t>Proceeds from reclamation deposits</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -25547,7 +25571,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">

--- a/output/pdf_financials_xlsx/SVG.xlsx
+++ b/output/pdf_financials_xlsx/SVG.xlsx
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.000389</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.022293</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -18605,7 +18605,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -22728,7 +22732,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>0.000389</v>
       </c>
